--- a/examples/attributes in dataset from TU Ilmenau.xlsx
+++ b/examples/attributes in dataset from TU Ilmenau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DEISM\DEISM_main\DEISM\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962F51FF-E8AA-4AB5-B496-B59B8175F852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040B52E4-79C1-4729-95AA-EFCEA1FE14B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="84">
   <si>
     <t>Attribute Name</t>
   </si>
@@ -349,6 +349,10 @@
   </si>
   <si>
     <t>louderspeaker as point source</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>letters represent numbers</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1028,12 +1032,12 @@
     <col min="4" max="4" width="11.9140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" style="2" customWidth="1"/>
     <col min="8" max="8" width="23.25" style="2" customWidth="1"/>
     <col min="9" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="38.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1046,6 +1050,9 @@
       </c>
       <c r="F1" s="8" t="s">
         <v>52</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
